--- a/e2e/expectedData/moju_Homestaff.xlsx
+++ b/e2e/expectedData/moju_Homestaff.xlsx
@@ -197,7 +197,7 @@
     <t>3,639.54</t>
   </si>
   <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>

--- a/e2e/expectedData/moju_Homestaff.xlsx
+++ b/e2e/expectedData/moju_Homestaff.xlsx
@@ -197,7 +197,7 @@
     <t>3,639.54</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
